--- a/cypress/fixtures/operations.xlsx
+++ b/cypress/fixtures/operations.xlsx
@@ -398,12 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,46 +413,95 @@
         <v>RESPONSE</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
         <v>GET</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>https://reqres.in/api/users?page=2</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2" t="str" xml:space="preserve">
+        <v xml:space="preserve">[
+  {
+    "id": 7,
+    "email": "michael.lawson@reqres.in",
+    "first_name": "Michael",
+    "last_name": "Lawson",
+    "avatar": "https://reqres.in/img/faces/7-image.jpg"
+  },
+  {
+    "id": 8,
+    "email": "lindsay.ferguson@reqres.in",
+    "first_name": "Lindsay",
+    "last_name": "Ferguson",
+    "avatar": "https://reqres.in/img/faces/8-image.jpg"
+  },
+  {
+    "id": 9,
+    "email": "tobias.funke@reqres.in",
+    "first_name": "Tobias",
+    "last_name": "Funke",
+    "avatar": "https://reqres.in/img/faces/9-image.jpg"
+  },
+  {
+    "id": 10,
+    "email": "byron.fields@reqres.in",
+    "first_name": "Byron",
+    "last_name": "Fields",
+    "avatar": "https://reqres.in/img/faces/10-image.jpg"
+  },
+  {
+    "id": 11,
+    "email": "george.edwards@reqres.in",
+    "first_name": "George",
+    "last_name": "Edwards",
+    "avatar": "https://reqres.in/img/faces/11-image.jpg"
+  },
+  {
+    "id": 12,
+    "email": "rachel.howell@reqres.in",
+    "first_name": "Rachel",
+    "last_name": "Howell",
+    "avatar": "https://reqres.in/img/faces/12-image.jpg"
+  }
+]</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>POST</v>
       </c>
       <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
+        <v>https://reqres.in/api/users</v>
+      </c>
+      <c r="C3" t="str" xml:space="preserve">
+        <v xml:space="preserve">{
+  "name": "Ethan",
+  "job": "tester"
+}</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>"Created"</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>PUT</v>
       </c>
       <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
+        <v>https://reqres.in/api/users/2</v>
+      </c>
+      <c r="C4" t="str" xml:space="preserve">
+        <v xml:space="preserve">{
+  "name": "morpheus",
+  "job": "zion resident"
+}</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>"OK"</v>
       </c>
     </row>
     <row r="5">
@@ -466,13 +509,13 @@
         <v>DELETE</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>https://reqres.in/api/users/2</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
